--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
+          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type, AND on any fleet sharing a Catchability_index group whose q is estimated, even with no index_data of its own -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. A shared group starts at the geometric mean of its members' values, so one blank or zero seeds the WHOLE group at NA or -Inf and it cannot fit; build_map() warns. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Standard deviation for the q prior, on the log scale. Must be positive under Estimated-with-prior, where the prior is scored at it.</t>
+          <t>Standard deviation for the q prior, on the log scale. Must be positive under Estimated-with-prior, where the prior is scored at it. In a shared Catchability_index group only the LEAD fleet's is read, because the prior is scored once on the lead, so a differing value on a non-lead fleet has no effect.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ageing error matrix index, matching 'Ageing_error_index' in 'age_error'. Fleets sharing a value read the same matrix. Omit the column (or leave NA) to use the fleet's own species, which is what a model with one matrix per species has always done. Give a fleet its own index when its otoliths were read by a method that ages them differently -- an ageing protocol that changed part way through a series is the usual case, and the two eras are then separate fleets sharing a Selectivity_index.</t>
+          <t>Ageing error matrix index, matching 'Ageing_error_index' in 'age_error'. Fleets sharing a value read the same matrix. Omit the column (or leave NA) to use the fleet's own species, which is what a model with one matrix per species has always done -- valid only while 'age_error' is itself indexed by species, since the fallback is the species number; data_check() refuses it once the indices mean something else. Give a fleet its own index when its otoliths were read by a method that ages them differently -- an ageing protocol that changed part way through a series is the usual case, and the two eras are then separate fleets sharing a Selectivity_index.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1437,7 +1437,7 @@
 0 or "Fixed" = fixed at Catchability_init_x000D_
 1 or "Estimated" = estimate as a free parameter_x000D_
 2 or "Estimated-with-prior" = estimate with a lognormal prior on q, mean Catchability_init (median when bias_adjust_proc = FALSE) and log-scale SD Catchability_prior_sd_x000D_
-3 or "Analytical" = geometric-mean analytical q following Ludwig and Walters 1994_x000D_
+3 or "Analytical" = geometric-mean analytical q following Walters and Ludwig 1994_x000D_
 4 or "PowerEquation" = power equation (NOT YET IMPLEMENTED)_x000D_
 5 or "Environmental" = linear equation log(q_y) = q_mu + beta * index_y; the environmental index is specified by Time_varying_q_x000D_
 6 or "AR1" = REMOVED; data_check() errors. The deviates were never estimated, so q came back constant. Express the Rogers et al. (2024) form as a q linkage with ar1(1 | Year) and 'observe'; the error gives the call._x000D_
@@ -1557,7 +1557,7 @@
         <is>
           <t>0 = use input "Log_sd" from index_data_x000D_
 1 = estimate as free parameter_x000D_
-2 = estimate analytically following Ludwig and Walters (1994)</t>
+2 = estimate analytically following Walters and Ludwig (1994)</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
         <is>
           <t>0 = use input "Log_sd" from catch_data_x000D_
 1 = estimate as free parameter_x000D_
-2 = estimate analytically following Ludwig and Walters (1994)</t>
+2 = estimate analytically following Walters and Ludwig (1994)</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
+          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5; always read by the 2DAR1 and 3DAR1 forms, as the conditional sd of their deviation field.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5; always read by the 2DAR1 and 3DAR1 forms, as the conditional sd of their deviation field.</t>
+          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5; required by the 2DAR1 and 3DAR1 forms, which read it as the conditional sd of their deviation field.</t>
         </is>
       </c>
     </row>
